--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.34427</v>
+        <v>17.69417</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1966</v>
+        <v>17.28855</v>
       </c>
       <c r="E2" t="n">
-        <v>17.39146</v>
+        <v>17.69411</v>
       </c>
       <c r="F2" t="n">
-        <v>45.28796</v>
+        <v>43.571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05229</v>
+        <v>0.0525</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92186</v>
+        <v>1.89033</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.94711</v>
+        <v>17.8407</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90758</v>
+        <v>17.60089</v>
       </c>
       <c r="E3" t="n">
-        <v>17.7065</v>
+        <v>17.62087</v>
       </c>
       <c r="F3" t="n">
-        <v>44.88557</v>
+        <v>44.04745</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05173</v>
+        <v>0.05267</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95474</v>
+        <v>1.9037</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.92643</v>
+        <v>17.67372</v>
       </c>
       <c r="D4" t="n">
-        <v>16.97254</v>
+        <v>17.37808</v>
       </c>
       <c r="E4" t="n">
-        <v>17.6274</v>
+        <v>17.61074</v>
       </c>
       <c r="F4" t="n">
-        <v>45.0123</v>
+        <v>43.85901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0535</v>
+        <v>0.05215</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92865</v>
+        <v>1.90883</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.83565</v>
+        <v>17.52014</v>
       </c>
       <c r="D6" t="n">
-        <v>16.96934</v>
+        <v>16.79122</v>
       </c>
       <c r="E6" t="n">
-        <v>16.90013</v>
+        <v>17.23741</v>
       </c>
       <c r="F6" t="n">
-        <v>22.35188</v>
+        <v>22.86021</v>
       </c>
       <c r="G6" t="n">
-        <v>36.27689</v>
+        <v>35.32782</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.47414</v>
+        <v>17.42261</v>
       </c>
       <c r="D7" t="n">
-        <v>16.97829</v>
+        <v>16.35286</v>
       </c>
       <c r="E7" t="n">
-        <v>17.12319</v>
+        <v>17.17959</v>
       </c>
       <c r="F7" t="n">
-        <v>22.79178</v>
+        <v>22.85849</v>
       </c>
       <c r="G7" t="n">
-        <v>35.46505</v>
+        <v>35.74811</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.4697</v>
+        <v>17.69935</v>
       </c>
       <c r="D8" t="n">
-        <v>16.71143</v>
+        <v>16.43343</v>
       </c>
       <c r="E8" t="n">
-        <v>16.93489</v>
+        <v>17.35618</v>
       </c>
       <c r="F8" t="n">
-        <v>22.43523</v>
+        <v>22.7823</v>
       </c>
       <c r="G8" t="n">
-        <v>35.26714</v>
+        <v>36.16068</v>
       </c>
     </row>
   </sheetData>
